--- a/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_20.xlsx
+++ b/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_20.xlsx
@@ -667,7 +667,7 @@
     <t>Krstovic</t>
   </si>
   <si>
-    <t>D'aversa</t>
+    <t>D'Aversa</t>
   </si>
   <si>
     <t>Milan</t>
@@ -727,7 +727,7 @@
     <t>Sorrentino A.</t>
   </si>
   <si>
-    <t>D'ambrosio</t>
+    <t>D'Ambrosio</t>
   </si>
   <si>
     <t>Pereira P.</t>

--- a/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_20.xlsx
+++ b/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_20.xlsx
@@ -667,7 +667,7 @@
     <t>Krstovic</t>
   </si>
   <si>
-    <t>D'aversa</t>
+    <t>D'Aversa</t>
   </si>
   <si>
     <t>Milan</t>
@@ -727,7 +727,7 @@
     <t>Sorrentino A.</t>
   </si>
   <si>
-    <t>D'ambrosio</t>
+    <t>D'Ambrosio</t>
   </si>
   <si>
     <t>Pereira P.</t>
@@ -2305,8 +2305,8 @@
       <c r="J29" s="10">
         <v>0</v>
       </c>
-      <c r="K29" s="10">
-        <v>0</v>
+      <c r="K29" s="1">
+        <v>1</v>
       </c>
       <c r="L29" s="10">
         <v>0</v>
@@ -3101,8 +3101,8 @@
       <c r="J49" s="10">
         <v>0</v>
       </c>
-      <c r="K49" s="1">
-        <v>1</v>
+      <c r="K49" s="10">
+        <v>0</v>
       </c>
       <c r="L49" s="10">
         <v>0</v>
@@ -17114,8 +17114,8 @@
       <c r="J29" s="10">
         <v>0</v>
       </c>
-      <c r="K29" s="10">
-        <v>0</v>
+      <c r="K29" s="1">
+        <v>1</v>
       </c>
       <c r="L29" s="10">
         <v>0</v>
@@ -17910,8 +17910,8 @@
       <c r="J49" s="10">
         <v>0</v>
       </c>
-      <c r="K49" s="1">
-        <v>1</v>
+      <c r="K49" s="10">
+        <v>0</v>
       </c>
       <c r="L49" s="10">
         <v>0</v>
@@ -31923,8 +31923,8 @@
       <c r="J29" s="10">
         <v>0</v>
       </c>
-      <c r="K29" s="10">
-        <v>0</v>
+      <c r="K29" s="1">
+        <v>1</v>
       </c>
       <c r="L29" s="10">
         <v>0</v>
@@ -32719,8 +32719,8 @@
       <c r="J49" s="10">
         <v>0</v>
       </c>
-      <c r="K49" s="1">
-        <v>1</v>
+      <c r="K49" s="10">
+        <v>0</v>
       </c>
       <c r="L49" s="10">
         <v>0</v>
